--- a/IncreasedSamplingMRUCache/OverallStatsIncreasedSamplingMRUCache-noboot.xlsx
+++ b/IncreasedSamplingMRUCache/OverallStatsIncreasedSamplingMRUCache-noboot.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alexb\OneDrive\Documents\Thesis\IncreasedSamplingMRUCache\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{050D9CEC-27C3-4786-A138-80D5FD197223}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43484C96-1E25-4DF0-93E3-C77317AC3EC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3380" yWindow="3380" windowWidth="28800" windowHeight="14460" xr2:uid="{84A3B88E-B226-40B3-A64E-0FDCC502A4B5}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{84A3B88E-B226-40B3-A64E-0FDCC502A4B5}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,10 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
-  <si>
-    <t>HalfCache</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t>Program</t>
   </si>
@@ -467,7 +464,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{652EE7E4-9A64-4328-97BF-22E9AA604A6A}">
-  <dimension ref="A1:M13"/>
+  <dimension ref="A2:M13"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="34.36328125" customWidth="1"/>
@@ -476,58 +473,53 @@
     <col min="11" max="11" width="14.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-    </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" t="s">
         <v>5</v>
       </c>
-      <c r="D2" t="s">
+      <c r="F2" t="s">
         <v>7</v>
       </c>
-      <c r="E2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>8</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
+        <v>11</v>
+      </c>
+      <c r="I2" t="s">
+        <v>12</v>
+      </c>
+      <c r="J2" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" t="s">
         <v>9</v>
       </c>
-      <c r="H2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I2" t="s">
-        <v>13</v>
-      </c>
-      <c r="J2" t="s">
-        <v>14</v>
-      </c>
-      <c r="K2" t="s">
-        <v>15</v>
-      </c>
-      <c r="L2" t="s">
+      <c r="M2" t="s">
         <v>10</v>
-      </c>
-      <c r="M2" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C5">
         <v>0</v>
@@ -569,10 +561,10 @@
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C10">
         <v>1</v>
@@ -614,10 +606,10 @@
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B13" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C13">
         <v>1</v>
